--- a/Adivinanzas_Estudiantes_Padlet.xlsx
+++ b/Adivinanzas_Estudiantes_Padlet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alumno_invitado\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FAEAF64-00D4-4EB7-A4DE-BF4A87B04AA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19CA4F9A-8371-4BF1-B113-5CCD4EC495C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="58">
   <si>
     <t>NOMBRE DEL ESTUDIANTE</t>
   </si>
@@ -183,13 +183,76 @@
   </si>
   <si>
     <t>Ambulancia</t>
+  </si>
+  <si>
+    <t>Auto.png</t>
+  </si>
+  <si>
+    <t>Archivo_pista</t>
+  </si>
+  <si>
+    <t>Pista_Auto</t>
+  </si>
+  <si>
+    <t>Pista_Avion</t>
+  </si>
+  <si>
+    <t>Pista_Barco</t>
+  </si>
+  <si>
+    <t>Archivo_imagen</t>
+  </si>
+  <si>
+    <t>Pista_Helicoptero</t>
+  </si>
+  <si>
+    <t>Pista_Tren</t>
+  </si>
+  <si>
+    <t>Pista_Submarino</t>
+  </si>
+  <si>
+    <t>Pista_Bicicleta</t>
+  </si>
+  <si>
+    <t>Pista_Monopatin</t>
+  </si>
+  <si>
+    <t>Pista_Camion</t>
+  </si>
+  <si>
+    <t>Pista_Avion_Tahiel.</t>
+  </si>
+  <si>
+    <t>Pista_Cohete</t>
+  </si>
+  <si>
+    <t>Pista_Ambulancia</t>
+  </si>
+  <si>
+    <t>Pista_Submarino_Milena</t>
+  </si>
+  <si>
+    <t>Submarino_Milena</t>
+  </si>
+  <si>
+    <t>Avion_Tahiel</t>
+  </si>
+  <si>
+    <t>Camion</t>
+  </si>
+  <si>
+    <t>Monopatin</t>
+  </si>
+  <si>
+    <t>Avion</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -212,6 +275,12 @@
     <font>
       <sz val="10"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="5">
@@ -240,7 +309,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -263,11 +332,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFC4C7C5"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFC4C7C5"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFC4C7C5"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFC4C7C5"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -283,6 +367,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -586,14 +673,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
     <col min="2" max="2" width="65" customWidth="1"/>
+    <col min="4" max="4" width="23.85546875" customWidth="1"/>
+    <col min="5" max="5" width="19.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -603,8 +692,14 @@
       <c r="C1" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
@@ -614,8 +709,14 @@
       <c r="C2" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D2" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>4</v>
       </c>
@@ -625,8 +726,14 @@
       <c r="C3" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D3" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
@@ -636,8 +743,14 @@
       <c r="C4" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D4" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>8</v>
       </c>
@@ -647,8 +760,14 @@
       <c r="C5" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D5" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
@@ -658,8 +777,14 @@
       <c r="C6" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D6" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>10</v>
       </c>
@@ -669,8 +794,14 @@
       <c r="C7" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D7" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>13</v>
       </c>
@@ -680,8 +811,14 @@
       <c r="C8" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D8" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>13</v>
       </c>
@@ -691,8 +828,14 @@
       <c r="C9" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D9" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>16</v>
       </c>
@@ -702,8 +845,14 @@
       <c r="C10" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D10" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>18</v>
       </c>
@@ -713,8 +862,14 @@
       <c r="C11" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D11" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>18</v>
       </c>
@@ -724,8 +879,14 @@
       <c r="C12" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D12" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>21</v>
       </c>
@@ -735,8 +896,14 @@
       <c r="C13" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D13" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>23</v>
       </c>
@@ -745,6 +912,12 @@
       </c>
       <c r="C14" t="s">
         <v>31</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>
